--- a/有父体1.0合并表/合并表.xlsx
+++ b/有父体1.0合并表/合并表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12315" windowHeight="9525"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="812">
   <si>
     <t>TemplateType=fptcustom</t>
   </si>
@@ -2463,30 +2463,6 @@
   </si>
   <si>
     <t>pricing_action</t>
-  </si>
-  <si>
-    <t>HM-HG-2P-CZS-902-1</t>
-  </si>
-  <si>
-    <t>PartialUpdate</t>
-  </si>
-  <si>
-    <t>B0CZDJ8RMW</t>
-  </si>
-  <si>
-    <t>ASIN</t>
-  </si>
-  <si>
-    <t>HM-HG-2+3+4P-0821</t>
-  </si>
-  <si>
-    <t>Child</t>
-  </si>
-  <si>
-    <t>StyleName</t>
-  </si>
-  <si>
-    <t>2Pack-A30</t>
   </si>
 </sst>
 </file>
@@ -3699,7 +3675,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:QC46"/>
+  <dimension ref="A1:QC45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="5" max="8" width="9" hidden="1" customWidth="1"/>
@@ -6858,23 +6834,15 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:445">
       <c r="A4" s="5"/>
-      <c r="B4" s="5" t="s">
-        <v>812</v>
-      </c>
+      <c r="B4" s="5"/>
       <c r="C4" s="5"/>
-      <c r="D4" s="6" t="s">
-        <v>813</v>
-      </c>
+      <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="5" t="s">
-        <v>814</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>815</v>
-      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
@@ -6900,18 +6868,10 @@
       <c r="AG4" s="6"/>
       <c r="AH4" s="6"/>
       <c r="AI4" s="5"/>
-      <c r="AJ4" s="5" t="s">
-        <v>816</v>
-      </c>
-      <c r="AK4" s="5" t="s">
-        <v>817</v>
-      </c>
-      <c r="AL4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM4" s="6" t="s">
-        <v>818</v>
-      </c>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="6"/>
       <c r="AN4" s="6"/>
       <c r="AO4" s="6"/>
       <c r="AP4" s="6"/>
@@ -6926,9 +6886,7 @@
       <c r="AY4" s="5"/>
       <c r="AZ4" s="6"/>
       <c r="BA4" s="6"/>
-      <c r="BB4" s="6" t="s">
-        <v>819</v>
-      </c>
+      <c r="BB4" s="6"/>
       <c r="BC4" s="6"/>
       <c r="BD4" s="5"/>
       <c r="BE4" s="5"/>
@@ -16261,7 +16219,7 @@
       <c r="QB24" s="21"/>
       <c r="QC24" s="21"/>
     </row>
-    <row r="25" s="1" customFormat="1" spans="1:445">
+    <row r="25" spans="1:82">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -16344,369 +16302,6 @@
       <c r="CB25" s="6"/>
       <c r="CC25" s="6"/>
       <c r="CD25" s="6"/>
-      <c r="CE25" s="21"/>
-      <c r="CF25" s="21"/>
-      <c r="CG25" s="21"/>
-      <c r="CH25" s="21"/>
-      <c r="CI25" s="21"/>
-      <c r="CJ25" s="21"/>
-      <c r="CK25" s="21"/>
-      <c r="CL25" s="21"/>
-      <c r="CM25" s="21"/>
-      <c r="CN25" s="21"/>
-      <c r="CO25" s="21"/>
-      <c r="CP25" s="21"/>
-      <c r="CQ25" s="21"/>
-      <c r="CR25" s="21"/>
-      <c r="CS25" s="21"/>
-      <c r="CT25" s="21"/>
-      <c r="CU25" s="21"/>
-      <c r="CV25" s="21"/>
-      <c r="CW25" s="21"/>
-      <c r="CX25" s="21"/>
-      <c r="CY25" s="21"/>
-      <c r="CZ25" s="21"/>
-      <c r="DA25" s="21"/>
-      <c r="DB25" s="21"/>
-      <c r="DC25" s="21"/>
-      <c r="DD25" s="21"/>
-      <c r="DE25" s="21"/>
-      <c r="DF25" s="21"/>
-      <c r="DG25" s="21"/>
-      <c r="DH25" s="21"/>
-      <c r="DI25" s="21"/>
-      <c r="DJ25" s="21"/>
-      <c r="DK25" s="21"/>
-      <c r="DL25" s="21"/>
-      <c r="DM25" s="21"/>
-      <c r="DN25" s="22"/>
-      <c r="DO25" s="22"/>
-      <c r="DP25" s="21"/>
-      <c r="DQ25" s="22"/>
-      <c r="DR25" s="22"/>
-      <c r="DS25" s="22"/>
-      <c r="DT25" s="22"/>
-      <c r="DU25" s="21"/>
-      <c r="DV25" s="21"/>
-      <c r="DW25" s="21"/>
-      <c r="DX25" s="21"/>
-      <c r="DY25" s="21"/>
-      <c r="DZ25" s="21"/>
-      <c r="EA25" s="21"/>
-      <c r="EB25" s="21"/>
-      <c r="EC25" s="21"/>
-      <c r="ED25" s="21"/>
-      <c r="EE25" s="21"/>
-      <c r="EF25" s="21"/>
-      <c r="EG25" s="21"/>
-      <c r="EH25" s="21"/>
-      <c r="EI25" s="21"/>
-      <c r="EJ25" s="21"/>
-      <c r="EK25" s="21"/>
-      <c r="EL25" s="21"/>
-      <c r="EM25" s="21"/>
-      <c r="EN25" s="21"/>
-      <c r="EO25" s="21"/>
-      <c r="EP25" s="21"/>
-      <c r="EQ25" s="21"/>
-      <c r="ER25" s="21"/>
-      <c r="ES25" s="21"/>
-      <c r="ET25" s="21"/>
-      <c r="EU25" s="21"/>
-      <c r="EV25" s="21"/>
-      <c r="EW25" s="21"/>
-      <c r="EX25" s="21"/>
-      <c r="EY25" s="21"/>
-      <c r="EZ25" s="27"/>
-      <c r="FA25" s="21"/>
-      <c r="FB25" s="21"/>
-      <c r="FC25" s="21"/>
-      <c r="FD25" s="21"/>
-      <c r="FE25" s="21"/>
-      <c r="FF25" s="21"/>
-      <c r="FG25" s="21"/>
-      <c r="FH25" s="21"/>
-      <c r="FI25" s="21"/>
-      <c r="FJ25" s="21"/>
-      <c r="FK25" s="21"/>
-      <c r="FL25" s="21"/>
-      <c r="FM25" s="21"/>
-      <c r="FN25" s="21"/>
-      <c r="FO25" s="21"/>
-      <c r="FP25" s="21"/>
-      <c r="FQ25" s="21"/>
-      <c r="FR25" s="21"/>
-      <c r="FS25" s="21"/>
-      <c r="FT25" s="21"/>
-      <c r="FU25" s="21"/>
-      <c r="FV25" s="21"/>
-      <c r="FW25" s="21"/>
-      <c r="FX25" s="21"/>
-      <c r="FY25" s="21"/>
-      <c r="FZ25" s="21"/>
-      <c r="GA25" s="21"/>
-      <c r="GB25" s="21"/>
-      <c r="GC25" s="21"/>
-      <c r="GD25" s="21"/>
-      <c r="GE25" s="21"/>
-      <c r="GF25" s="21"/>
-      <c r="GG25" s="21"/>
-      <c r="GH25" s="21"/>
-      <c r="GI25" s="21"/>
-      <c r="GJ25" s="21"/>
-      <c r="GK25" s="21"/>
-      <c r="GL25" s="21"/>
-      <c r="GM25" s="21"/>
-      <c r="GN25" s="22"/>
-      <c r="GO25" s="21"/>
-      <c r="GP25" s="21"/>
-      <c r="GQ25" s="21"/>
-      <c r="GR25" s="21"/>
-      <c r="GS25" s="21"/>
-      <c r="GT25" s="21"/>
-      <c r="GU25" s="21"/>
-      <c r="GV25" s="21"/>
-      <c r="GW25" s="21"/>
-      <c r="GX25" s="22"/>
-      <c r="GY25" s="22"/>
-      <c r="GZ25" s="21"/>
-      <c r="HA25" s="22"/>
-      <c r="HB25" s="21"/>
-      <c r="HC25" s="21"/>
-      <c r="HD25" s="21"/>
-      <c r="HE25" s="21"/>
-      <c r="HF25" s="21"/>
-      <c r="HG25" s="21"/>
-      <c r="HH25" s="21"/>
-      <c r="HI25" s="21"/>
-      <c r="HJ25" s="21"/>
-      <c r="HK25" s="21"/>
-      <c r="HL25" s="21"/>
-      <c r="HM25" s="21"/>
-      <c r="HN25" s="21"/>
-      <c r="HO25" s="22"/>
-      <c r="HP25" s="22"/>
-      <c r="HQ25" s="22"/>
-      <c r="HR25" s="21"/>
-      <c r="HS25" s="21"/>
-      <c r="HT25" s="22"/>
-      <c r="HU25" s="21"/>
-      <c r="HV25" s="21"/>
-      <c r="HW25" s="21"/>
-      <c r="HX25" s="22"/>
-      <c r="HY25" s="21"/>
-      <c r="HZ25" s="22"/>
-      <c r="IA25" s="21"/>
-      <c r="IB25" s="21"/>
-      <c r="IC25" s="21"/>
-      <c r="ID25" s="22"/>
-      <c r="IE25" s="22"/>
-      <c r="IF25" s="22"/>
-      <c r="IG25" s="21"/>
-      <c r="IH25" s="22"/>
-      <c r="II25" s="22"/>
-      <c r="IJ25" s="21"/>
-      <c r="IK25" s="21"/>
-      <c r="IL25" s="22"/>
-      <c r="IM25" s="22"/>
-      <c r="IN25" s="22"/>
-      <c r="IO25" s="21"/>
-      <c r="IP25" s="22"/>
-      <c r="IQ25" s="21"/>
-      <c r="IR25" s="22"/>
-      <c r="IS25" s="22"/>
-      <c r="IT25" s="21"/>
-      <c r="IU25" s="21"/>
-      <c r="IV25" s="22"/>
-      <c r="IW25" s="21"/>
-      <c r="IX25" s="22"/>
-      <c r="IY25" s="21"/>
-      <c r="IZ25" s="22"/>
-      <c r="JA25" s="21"/>
-      <c r="JB25" s="22"/>
-      <c r="JC25" s="21"/>
-      <c r="JD25" s="22"/>
-      <c r="JE25" s="21"/>
-      <c r="JF25" s="22"/>
-      <c r="JG25" s="22"/>
-      <c r="JH25" s="22"/>
-      <c r="JI25" s="22"/>
-      <c r="JJ25" s="21"/>
-      <c r="JK25" s="21"/>
-      <c r="JL25" s="21"/>
-      <c r="JM25" s="21"/>
-      <c r="JN25" s="21"/>
-      <c r="JO25" s="21"/>
-      <c r="JP25" s="21"/>
-      <c r="JQ25" s="21"/>
-      <c r="JR25" s="21"/>
-      <c r="JS25" s="21"/>
-      <c r="JT25" s="21"/>
-      <c r="JU25" s="21"/>
-      <c r="JV25" s="21"/>
-      <c r="JW25" s="21"/>
-      <c r="JX25" s="22"/>
-      <c r="JY25" s="21"/>
-      <c r="JZ25" s="22"/>
-      <c r="KA25" s="22"/>
-      <c r="KB25" s="22"/>
-      <c r="KC25" s="21"/>
-      <c r="KD25" s="21"/>
-      <c r="KE25" s="21"/>
-      <c r="KF25" s="21"/>
-      <c r="KG25" s="21"/>
-      <c r="KH25" s="21"/>
-      <c r="KI25" s="21"/>
-      <c r="KJ25" s="21"/>
-      <c r="KK25" s="21"/>
-      <c r="KL25" s="21"/>
-      <c r="KM25" s="21"/>
-      <c r="KN25" s="21"/>
-      <c r="KO25" s="21"/>
-      <c r="KP25" s="21"/>
-      <c r="KQ25" s="21"/>
-      <c r="KR25" s="21"/>
-      <c r="KS25" s="22"/>
-      <c r="KT25" s="21"/>
-      <c r="KU25" s="21"/>
-      <c r="KV25" s="21"/>
-      <c r="KW25" s="21"/>
-      <c r="KX25" s="21"/>
-      <c r="KY25" s="21"/>
-      <c r="KZ25" s="44"/>
-      <c r="LA25" s="44"/>
-      <c r="LB25" s="44"/>
-      <c r="LC25" s="22"/>
-      <c r="LD25" s="21"/>
-      <c r="LE25" s="22"/>
-      <c r="LF25" s="21"/>
-      <c r="LG25" s="44"/>
-      <c r="LH25" s="44"/>
-      <c r="LI25" s="21"/>
-      <c r="LJ25" s="21"/>
-      <c r="LK25" s="21"/>
-      <c r="LL25" s="22"/>
-      <c r="LM25" s="21"/>
-      <c r="LN25" s="21"/>
-      <c r="LO25" s="21"/>
-      <c r="LP25" s="21"/>
-      <c r="LQ25" s="21"/>
-      <c r="LR25" s="21"/>
-      <c r="LS25" s="21"/>
-      <c r="LT25" s="21"/>
-      <c r="LU25" s="21"/>
-      <c r="LV25" s="22"/>
-      <c r="LW25" s="21"/>
-      <c r="LX25" s="21"/>
-      <c r="LY25" s="21"/>
-      <c r="LZ25" s="21"/>
-      <c r="MA25" s="22"/>
-      <c r="MB25" s="21"/>
-      <c r="MC25" s="21"/>
-      <c r="MD25" s="21"/>
-      <c r="ME25" s="21"/>
-      <c r="MF25" s="21"/>
-      <c r="MG25" s="21"/>
-      <c r="MH25" s="21"/>
-      <c r="MI25" s="21"/>
-      <c r="MJ25" s="21"/>
-      <c r="MK25" s="21"/>
-      <c r="ML25" s="21"/>
-      <c r="MM25" s="21"/>
-      <c r="MN25" s="21"/>
-      <c r="MO25" s="21"/>
-      <c r="MP25" s="21"/>
-      <c r="MQ25" s="21"/>
-      <c r="MR25" s="21"/>
-      <c r="MS25" s="21"/>
-      <c r="MT25" s="21"/>
-      <c r="MU25" s="21"/>
-      <c r="MV25" s="21"/>
-      <c r="MW25" s="21"/>
-      <c r="MX25" s="21"/>
-      <c r="MY25" s="21"/>
-      <c r="MZ25" s="21"/>
-      <c r="NA25" s="21"/>
-      <c r="NB25" s="21"/>
-      <c r="NC25" s="21"/>
-      <c r="ND25" s="21"/>
-      <c r="NE25" s="21"/>
-      <c r="NF25" s="21"/>
-      <c r="NG25" s="21"/>
-      <c r="NH25" s="21"/>
-      <c r="NI25" s="21"/>
-      <c r="NJ25" s="21"/>
-      <c r="NK25" s="21"/>
-      <c r="NL25" s="21"/>
-      <c r="NM25" s="21"/>
-      <c r="NN25" s="21"/>
-      <c r="NO25" s="21"/>
-      <c r="NP25" s="21"/>
-      <c r="NQ25" s="21"/>
-      <c r="NR25" s="21"/>
-      <c r="NS25" s="21"/>
-      <c r="NT25" s="21"/>
-      <c r="NU25" s="21"/>
-      <c r="NV25" s="21"/>
-      <c r="NW25" s="21"/>
-      <c r="NX25" s="21"/>
-      <c r="NY25" s="21"/>
-      <c r="NZ25" s="21"/>
-      <c r="OA25" s="21"/>
-      <c r="OB25" s="21"/>
-      <c r="OC25" s="21"/>
-      <c r="OD25" s="21"/>
-      <c r="OE25" s="22"/>
-      <c r="OF25" s="21"/>
-      <c r="OG25" s="21"/>
-      <c r="OH25" s="27"/>
-      <c r="OI25" s="27"/>
-      <c r="OJ25" s="27"/>
-      <c r="OK25" s="44"/>
-      <c r="OL25" s="22"/>
-      <c r="OM25" s="27"/>
-      <c r="ON25" s="44"/>
-      <c r="OO25" s="44"/>
-      <c r="OP25" s="27"/>
-      <c r="OQ25" s="21"/>
-      <c r="OR25" s="44"/>
-      <c r="OS25" s="21"/>
-      <c r="OT25" s="21"/>
-      <c r="OU25" s="21"/>
-      <c r="OV25" s="44"/>
-      <c r="OW25" s="27"/>
-      <c r="OX25" s="21"/>
-      <c r="OY25" s="22"/>
-      <c r="OZ25" s="21"/>
-      <c r="PA25" s="27"/>
-      <c r="PB25" s="21"/>
-      <c r="PC25" s="44"/>
-      <c r="PD25" s="21"/>
-      <c r="PE25" s="21"/>
-      <c r="PF25" s="22"/>
-      <c r="PG25" s="21"/>
-      <c r="PH25" s="22"/>
-      <c r="PI25" s="21"/>
-      <c r="PJ25" s="44"/>
-      <c r="PK25" s="22"/>
-      <c r="PL25" s="44"/>
-      <c r="PM25" s="22"/>
-      <c r="PN25" s="44"/>
-      <c r="PO25" s="22"/>
-      <c r="PP25" s="44"/>
-      <c r="PQ25" s="22"/>
-      <c r="PR25" s="44"/>
-      <c r="PS25" s="22"/>
-      <c r="PT25" s="21"/>
-      <c r="PU25" s="44"/>
-      <c r="PV25" s="22"/>
-      <c r="PW25" s="44"/>
-      <c r="PX25" s="22"/>
-      <c r="PY25" s="44"/>
-      <c r="PZ25" s="22"/>
-      <c r="QA25" s="21"/>
-      <c r="QB25" s="21"/>
-      <c r="QC25" s="21"/>
     </row>
     <row r="26" spans="1:82">
       <c r="A26" s="5"/>
@@ -18388,90 +17983,6 @@
       <c r="CC45" s="6"/>
       <c r="CD45" s="6"/>
     </row>
-    <row r="46" spans="1:82">
-      <c r="A46" s="5"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="6"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
-      <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="6"/>
-      <c r="Y46" s="6"/>
-      <c r="Z46" s="6"/>
-      <c r="AA46" s="6"/>
-      <c r="AB46" s="6"/>
-      <c r="AC46" s="6"/>
-      <c r="AD46" s="6"/>
-      <c r="AE46" s="6"/>
-      <c r="AF46" s="6"/>
-      <c r="AG46" s="6"/>
-      <c r="AH46" s="6"/>
-      <c r="AI46" s="5"/>
-      <c r="AJ46" s="5"/>
-      <c r="AK46" s="5"/>
-      <c r="AL46" s="5"/>
-      <c r="AM46" s="6"/>
-      <c r="AN46" s="6"/>
-      <c r="AO46" s="6"/>
-      <c r="AP46" s="6"/>
-      <c r="AQ46" s="6"/>
-      <c r="AR46" s="6"/>
-      <c r="AS46" s="6"/>
-      <c r="AT46" s="6"/>
-      <c r="AU46" s="6"/>
-      <c r="AV46" s="5"/>
-      <c r="AW46" s="5"/>
-      <c r="AX46" s="5"/>
-      <c r="AY46" s="5"/>
-      <c r="AZ46" s="6"/>
-      <c r="BA46" s="6"/>
-      <c r="BB46" s="6"/>
-      <c r="BC46" s="6"/>
-      <c r="BD46" s="5"/>
-      <c r="BE46" s="5"/>
-      <c r="BF46" s="6"/>
-      <c r="BG46" s="6"/>
-      <c r="BH46" s="6"/>
-      <c r="BI46" s="6"/>
-      <c r="BJ46" s="6"/>
-      <c r="BK46" s="6"/>
-      <c r="BL46" s="6"/>
-      <c r="BM46" s="6"/>
-      <c r="BN46" s="6"/>
-      <c r="BO46" s="6"/>
-      <c r="BP46" s="6"/>
-      <c r="BQ46" s="6"/>
-      <c r="BR46" s="6"/>
-      <c r="BS46" s="6"/>
-      <c r="BT46" s="6"/>
-      <c r="BU46" s="6"/>
-      <c r="BV46" s="6"/>
-      <c r="BW46" s="6"/>
-      <c r="BX46" s="6"/>
-      <c r="BY46" s="6"/>
-      <c r="BZ46" s="6"/>
-      <c r="CA46" s="6"/>
-      <c r="CB46" s="6"/>
-      <c r="CC46" s="6"/>
-      <c r="CD46" s="6"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
